--- a/DATA_DIPA/DIPA_2025.xlsx
+++ b/DATA_DIPA/DIPA_2025.xlsx
@@ -519,7 +519,7 @@
         <v>2025</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="E2" t="n">
         <v>12375659000</v>
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -579,7 +579,7 @@
         <v>2025</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="E3" t="n">
         <v>12050810000</v>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
         <v>2025</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="E4" t="n">
         <v>10550346000</v>
@@ -676,7 +676,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -699,7 +699,7 @@
         <v>2025</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="E5" t="n">
         <v>8190997000</v>
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
         <v>2025</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="E6" t="n">
         <v>509462000</v>
@@ -796,7 +796,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>2025</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="E7" t="n">
         <v>141148000</v>
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
         <v>2025</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="E8" t="n">
         <v>1324164000</v>
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
         <v>2025</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="E9" t="n">
         <v>28039697000</v>
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>2025</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="E10" t="n">
         <v>4632337000</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         <v>2025</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="E11" t="n">
         <v>3970295000</v>
@@ -1096,7 +1096,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         <v>2025</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="E12" t="n">
         <v>5487467000</v>
@@ -1156,7 +1156,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>2025</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="E13" t="n">
         <v>120000000</v>
@@ -1216,7 +1216,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>2025</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="E14" t="n">
         <v>145625000</v>
@@ -1276,7 +1276,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>2025</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="E15" t="n">
         <v>77600000</v>
@@ -1336,7 +1336,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
         <v>2025</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="E17" t="n">
         <v>7827726000</v>
@@ -1456,7 +1456,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>2025</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="E19" t="n">
         <v>8801554000</v>
@@ -1576,7 +1576,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>2025</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="E20" t="n">
         <v>51391610000</v>
@@ -1636,7 +1636,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         <v>2025</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="E21" t="n">
         <v>1531469000</v>
@@ -1696,7 +1696,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -1719,7 +1719,7 @@
         <v>2025</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="E22" t="n">
         <v>1014188000</v>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>2025</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="E23" t="n">
         <v>211890000</v>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
         <v>2025</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="E24" t="n">
         <v>241922000</v>
@@ -1876,7 +1876,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         <v>2025</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="E25" t="n">
         <v>593953000</v>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>2025</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="E26" t="n">
         <v>623700000</v>
@@ -1996,7 +1996,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
         <v>2025</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="E27" t="n">
         <v>4391962000</v>
@@ -2056,7 +2056,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         <v>2025</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="E28" t="n">
         <v>1563822000</v>
@@ -2116,7 +2116,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>2025</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="E29" t="n">
         <v>1403368000</v>
@@ -2176,7 +2176,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>2025</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="E30" t="n">
         <v>958882000</v>
@@ -2236,7 +2236,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         <v>2025</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="E31" t="n">
         <v>2141764000</v>
@@ -2296,7 +2296,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>2025</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="E32" t="n">
         <v>6856990000</v>
@@ -2356,7 +2356,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>2025</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="E33" t="n">
         <v>8433215000</v>
@@ -2416,7 +2416,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
         <v>2025</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="E34" t="n">
         <v>36221884000</v>
@@ -2476,7 +2476,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
         <v>2025</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="E35" t="n">
         <v>1846087000</v>
@@ -2536,7 +2536,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         <v>2025</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="E36" t="n">
         <v>1103429000</v>
@@ -2596,7 +2596,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>2025</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="E37" t="n">
         <v>35616000</v>
@@ -2656,7 +2656,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
         <v>2025</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="E38" t="n">
         <v>129934000</v>
@@ -2716,7 +2716,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         <v>2025</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="E39" t="n">
         <v>155798000</v>
@@ -2776,7 +2776,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>2025</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="E40" t="n">
         <v>2963001399000</v>
@@ -2836,7 +2836,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="N40" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         <v>2025</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="E41" t="n">
         <v>1566293000</v>
@@ -2896,7 +2896,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="N41" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>2025</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="E42" t="n">
         <v>482847000</v>
@@ -2956,7 +2956,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="N42" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>2025</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="E43" t="n">
         <v>964305000</v>
@@ -3016,7 +3016,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="N43" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>2025</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="E44" t="n">
         <v>792272000</v>
@@ -3076,7 +3076,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="N44" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>2025</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="E45" t="n">
         <v>457836000</v>
@@ -3136,7 +3136,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>2025</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="E46" t="n">
         <v>433141000</v>
@@ -3196,7 +3196,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
         <v>2025</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="E47" t="n">
         <v>708494230000</v>
@@ -3256,7 +3256,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         <v>2025</v>
       </c>
       <c r="D49" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="E49" t="n">
         <v>72971395000</v>
@@ -3376,7 +3376,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         <v>2025</v>
       </c>
       <c r="D51" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="E51" t="n">
         <v>6636346000</v>
@@ -3496,7 +3496,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="N51" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
         <v>2025</v>
       </c>
       <c r="D52" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="E52" t="n">
         <v>6574074000</v>
@@ -3556,7 +3556,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="N52" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
         <v>2025</v>
       </c>
       <c r="D53" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="E53" t="n">
         <v>6614760000</v>
@@ -3616,7 +3616,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="N53" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         <v>2025</v>
       </c>
       <c r="D54" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="E54" t="n">
         <v>560040000</v>
@@ -3676,7 +3676,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="N54" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>2025</v>
       </c>
       <c r="D55" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="E55" t="n">
         <v>1380742000</v>
@@ -3736,7 +3736,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="N55" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         <v>2025</v>
       </c>
       <c r="D56" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="E56" t="n">
         <v>74069711000</v>
@@ -3796,7 +3796,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="N56" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         <v>2025</v>
       </c>
       <c r="D57" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="E57" t="n">
         <v>54790424000</v>
@@ -3856,7 +3856,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="N57" t="inlineStr">
         <is>
@@ -3879,7 +3879,7 @@
         <v>2025</v>
       </c>
       <c r="D58" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="E58" t="n">
         <v>57676148000</v>
@@ -3916,7 +3916,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="N58" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         <v>2025</v>
       </c>
       <c r="D59" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="E59" t="n">
         <v>2711331000</v>
@@ -3976,7 +3976,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="N59" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
         <v>2025</v>
       </c>
       <c r="D60" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="E60" t="n">
         <v>1642979000</v>
@@ -4036,7 +4036,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="N60" t="inlineStr">
         <is>
@@ -4059,7 +4059,7 @@
         <v>2025</v>
       </c>
       <c r="D61" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="E61" t="n">
         <v>305413000</v>
@@ -4096,7 +4096,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="N61" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         <v>2025</v>
       </c>
       <c r="D62" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="E62" t="n">
         <v>553160000</v>
@@ -4156,7 +4156,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="N62" t="inlineStr">
         <is>
@@ -4179,7 +4179,7 @@
         <v>2025</v>
       </c>
       <c r="D63" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="E63" t="n">
         <v>245582000</v>
@@ -4216,7 +4216,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="N63" t="inlineStr">
         <is>
@@ -4239,7 +4239,7 @@
         <v>2025</v>
       </c>
       <c r="D64" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="E64" t="n">
         <v>5244929000</v>
@@ -4276,7 +4276,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="N64" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         <v>2025</v>
       </c>
       <c r="D65" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="E65" t="n">
         <v>6730100000</v>
@@ -4336,7 +4336,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="N65" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>2025</v>
       </c>
       <c r="D66" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="E66" t="n">
         <v>7084301000</v>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="N66" t="inlineStr">
         <is>
@@ -4419,7 +4419,7 @@
         <v>2025</v>
       </c>
       <c r="D67" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="E67" t="n">
         <v>6943411000</v>
@@ -4456,7 +4456,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="N67" t="inlineStr">
         <is>
@@ -4479,7 +4479,7 @@
         <v>2025</v>
       </c>
       <c r="D68" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="E68" t="n">
         <v>40006172000</v>
@@ -4516,7 +4516,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="N68" t="inlineStr">
         <is>
@@ -4539,7 +4539,7 @@
         <v>2025</v>
       </c>
       <c r="D69" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="E69" t="n">
         <v>4503238000</v>
@@ -4576,7 +4576,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="N69" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         <v>2025</v>
       </c>
       <c r="D70" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="E70" t="n">
         <v>12792429000</v>
@@ -4636,7 +4636,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="N70" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>2025</v>
       </c>
       <c r="D71" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="E71" t="n">
         <v>3099494000</v>
@@ -4696,7 +4696,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="N71" t="inlineStr">
         <is>
@@ -4719,7 +4719,7 @@
         <v>2025</v>
       </c>
       <c r="D72" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="E72" t="n">
         <v>7539521000</v>
@@ -4756,7 +4756,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="N72" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         <v>2025</v>
       </c>
       <c r="D73" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="E73" t="n">
         <v>8818774000</v>
@@ -4816,7 +4816,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="N73" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         <v>2025</v>
       </c>
       <c r="D74" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="E74" t="n">
         <v>10076200000</v>
@@ -4876,7 +4876,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="N74" t="inlineStr">
         <is>
@@ -4899,7 +4899,7 @@
         <v>2025</v>
       </c>
       <c r="D75" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="E75" t="n">
         <v>2653374000</v>
@@ -4936,7 +4936,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="N75" t="inlineStr">
         <is>
@@ -4959,7 +4959,7 @@
         <v>2025</v>
       </c>
       <c r="D76" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="E76" t="n">
         <v>1628753000</v>
@@ -4996,7 +4996,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="N76" t="inlineStr">
         <is>
@@ -5019,7 +5019,7 @@
         <v>2025</v>
       </c>
       <c r="D77" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="E77" t="n">
         <v>624238186000</v>
@@ -5056,7 +5056,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="N77" t="inlineStr">
         <is>

--- a/DATA_DIPA/DIPA_2025.xlsx
+++ b/DATA_DIPA/DIPA_2025.xlsx
@@ -512,7 +512,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SATKER 007130</t>
+          <t>007130 - KEJAKSAAN NEGERI OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -572,7 +572,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SATKER 007190</t>
+          <t>007190 - KEJAKSAAN NEGERI OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -632,7 +632,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SATKER 007208</t>
+          <t>007208 - KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -692,7 +692,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SATKER 098963</t>
+          <t>098963 - PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -752,7 +752,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SATKER 099228</t>
+          <t>099228 - PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -812,7 +812,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SATKER 111071</t>
+          <t>111071 - KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -872,7 +872,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SATKER 111079</t>
+          <t>111079 - BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SATKER 344894</t>
+          <t>344894 - RUMKIT TK. III 02.06.02 DR. NOESMIR BATURAJA KESDAM II/SWJ</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -992,7 +992,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SATKER 401944</t>
+          <t>401944 - PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SATKER 401945</t>
+          <t>401945 - PENGADILAN AGAMA MUARADUA</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SATKER 402267</t>
+          <t>402267 - PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SATKER 402268</t>
+          <t>402268 - PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SATKER 403409</t>
+          <t>403409 - PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SATKER 403410</t>
+          <t>403410 - PENGADILAN AGAMA MUARADUA</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SATKER 406426</t>
+          <t>406426 - LAPAS KELAS IIB MUARA DUA</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SATKER 406472</t>
+          <t>406472 - RUMAH TAHANAN NEGARA BATURAJA</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SATKER 406488</t>
+          <t>406488 - LAPAS KELAS IIB MARTAPURA</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SATKER 410574</t>
+          <t>410574 - KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SATKER 418456</t>
+          <t>418456 - KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SATKER 418457</t>
+          <t>418457 - KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SATKER 418458</t>
+          <t>418458 - KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SATKER 418459</t>
+          <t>418459 - KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -1832,7 +1832,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SATKER 418461</t>
+          <t>418461 - KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SATKER 418462</t>
+          <t>418462 - MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SATKER 418471</t>
+          <t>418471 - MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -2012,7 +2012,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SATKER 419006</t>
+          <t>419006 - SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SATKER 424245</t>
+          <t>424245 - MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SATKER 424967</t>
+          <t>424967 - MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SATKER 426050</t>
+          <t>426050 - MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SATKER 426066</t>
+          <t>426066 - MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SATKER 428258</t>
+          <t>428258 - BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SATKER 431142</t>
+          <t>431142 - KANTOR PERTANAHAN KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SATKER 440502</t>
+          <t>440502 - KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SATKER 440503</t>
+          <t>440503 - KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SATKER 440504</t>
+          <t>440504 - KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SATKER 440505</t>
+          <t>440505 - KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SATKER 440506</t>
+          <t>440506 - KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -2732,7 +2732,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SATKER 440507</t>
+          <t>440507 - KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SATKER 500163</t>
+          <t>500163 - KPPN BATURAJA PENYALUR DANA TRANSFER UMUM</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -2852,7 +2852,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SATKER 527975</t>
+          <t>527975 - KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SATKER 553099</t>
+          <t>553099 - MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SATKER 553792</t>
+          <t>553792 - MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -3032,7 +3032,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SATKER 574370</t>
+          <t>574370 - MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SATKER 597480</t>
+          <t>597480 - MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SATKER 597558</t>
+          <t>597558 - MADRASAH ALIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -3212,7 +3212,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SATKER 600092</t>
+          <t>600092 - KPPN BATURAJA PENYALUR DANA TRANSFER KHUSUS</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -3272,7 +3272,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SATKER 632013</t>
+          <t>632013 - BAPAS KELAS II OKU INDUK</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SATKER 641681</t>
+          <t>641681 - POLRES OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SATKER 653271</t>
+          <t>653271 - RUMAH PENYIMPANAN BENDA SITAAN NEGARA BATURAJA</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -3452,7 +3452,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SATKER 656553</t>
+          <t>656553 - KPU  KABUPATEN OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>SATKER 656560</t>
+          <t>656560 - KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -3572,7 +3572,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SATKER 656574</t>
+          <t>656574 - KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SATKER 661192</t>
+          <t>661192 - MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -3692,7 +3692,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SATKER 662127</t>
+          <t>662127 - MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SATKER 665292</t>
+          <t>665292 - POLRES OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -3812,7 +3812,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>SATKER 665307</t>
+          <t>665307 - POLRES OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>SATKER 666501</t>
+          <t>666501 - KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SATKER 666502</t>
+          <t>666502 - KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -3992,7 +3992,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SATKER 666503</t>
+          <t>666503 - KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -4052,7 +4052,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SATKER 666504</t>
+          <t>666504 - KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SATKER 666505</t>
+          <t>666505 - KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SATKER 666507</t>
+          <t>666507 - KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -4232,7 +4232,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SATKER 667215</t>
+          <t>667215 - BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -4292,7 +4292,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SATKER 668529</t>
+          <t>668529 - BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -4352,7 +4352,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SATKER 669055</t>
+          <t>669055 - KANTOR PERTANAHAN KAB. OGAN KOMERING ULU TIMUR PROV. SUMATRA SELATAN</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SATKER 670561</t>
+          <t>670561 - KANTOR PERTANAHAN KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -4472,7 +4472,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SATKER 685001</t>
+          <t>685001 - PUSLATPUR KODIKLATAD</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -4532,7 +4532,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SATKER 686503</t>
+          <t>686503 - SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SATKER 690801</t>
+          <t>690801 - LOKA LABORATORIUM KESEHATAN MASYARAKAT BATURAJA</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -4652,7 +4652,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SATKER 691653</t>
+          <t>691653 - DINAS TENAGA KERJA DAN TRANSMIGRASI KABUPATEN OKU TIMUR</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SATKER 692334</t>
+          <t>692334 - LAPAS KELAS II B MUARA DUA</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SATKER 692339</t>
+          <t>692339 - RUTAN KELAS II B BATURAJA</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SATKER 692340</t>
+          <t>692340 - LAPAS KELAS II B MARTAPURA</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -4892,7 +4892,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SATKER 692625</t>
+          <t>692625 - BAPAS KELAS II OKU INDUK</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -4952,7 +4952,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SATKER 692725</t>
+          <t>692725 - RUPBASAN KELAS II BATURAJA</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -5012,7 +5012,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SATKER 700283</t>
+          <t>700283 - KPPN BATURAJA PENYALUR DANA DESA, INSENTIF FISKAL, OTONOMI KHUSUS DAN KEISTIMEWAAN</t>
         </is>
       </c>
       <c r="C77" t="n">
